--- a/02_Basic_Excel_for_Data_Analytics/17_Charts.xlsx
+++ b/02_Basic_Excel_for_Data_Analytics/17_Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01 COURSES\Learn_Data_Analytics_by_CWH\02_Basic_Excel_for_Data_Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20392E2B-130E-49E5-9807-713571212BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7D659A-1134-4926-AA7C-521C2EFE6ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Budget" sheetId="1" r:id="rId1"/>
@@ -5259,16 +5259,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>464032</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>140839</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>70760</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>72003</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>155816</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>125073</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>388472</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>56237</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
